--- a/public/samples/ja/sample2.xlsx
+++ b/public/samples/ja/sample2.xlsx
@@ -569,7 +569,7 @@
         <v>名前</v>
       </c>
       <c r="C2" s="3" t="str">
-        <v>性別♀</v>
+        <v>性別</v>
       </c>
       <c r="D2" s="3" t="str">
         <v>学習支援</v>
@@ -601,7 +601,7 @@
         <v>田中 綾香</v>
       </c>
       <c r="C3" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D3" s="3" t="str">
         <v>○</v>
@@ -617,6 +617,9 @@
       <c r="B4" s="3" t="str">
         <v>山本 武志</v>
       </c>
+      <c r="C4" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D4" s="3" t="str">
         <v>○</v>
       </c>
@@ -632,7 +635,7 @@
         <v>鈴木 美里</v>
       </c>
       <c r="C5" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E5" s="3" t="str">
         <v>○</v>
@@ -652,7 +655,7 @@
         <v>佐藤 可奈子</v>
       </c>
       <c r="C6" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G6" s="3" t="str">
         <v>○</v>
@@ -668,6 +671,9 @@
       <c r="B7" s="3" t="str">
         <v>伊藤 弘樹</v>
       </c>
+      <c r="C7" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G7" s="3" t="str">
         <v>◎</v>
       </c>
@@ -682,6 +688,9 @@
       <c r="B8" s="3" t="str">
         <v>小林 優太</v>
       </c>
+      <c r="C8" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J8" s="2">
         <v>86</v>
       </c>
@@ -693,6 +702,9 @@
       <c r="B9" s="3" t="str">
         <v>中村 芽衣</v>
       </c>
+      <c r="C9" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G9" s="3" t="str">
         <v>○</v>
       </c>
@@ -707,6 +719,9 @@
       <c r="B10" s="3" t="str">
         <v>加藤 信次</v>
       </c>
+      <c r="C10" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="H10" s="3" t="str">
         <v>〇</v>
       </c>
@@ -722,7 +737,7 @@
         <v>斉藤 まどか</v>
       </c>
       <c r="C11" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J11" s="2">
         <v>87</v>
@@ -735,6 +750,9 @@
       <c r="B12" s="3" t="str">
         <v>三浦 太一</v>
       </c>
+      <c r="C12" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D12" s="3" t="str">
         <v>○</v>
       </c>
@@ -750,7 +768,7 @@
         <v>高橋 直美</v>
       </c>
       <c r="C13" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G13" s="3" t="str">
         <v>○</v>
@@ -766,6 +784,9 @@
       <c r="B14" s="3" t="str">
         <v>林 健治</v>
       </c>
+      <c r="C14" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J14" s="2">
         <v>76</v>
       </c>
@@ -777,6 +798,9 @@
       <c r="B15" s="3" t="str">
         <v>渡辺 明良</v>
       </c>
+      <c r="C15" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F15" s="3" t="str">
         <v>○</v>
       </c>
@@ -791,6 +815,9 @@
       <c r="B16" s="3" t="str">
         <v>森田 愛</v>
       </c>
+      <c r="C16" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="E16" s="3" t="str">
         <v>○</v>
       </c>
@@ -805,6 +832,9 @@
       <c r="B17" s="3" t="str">
         <v>山田 孝史</v>
       </c>
+      <c r="C17" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J17" s="2">
         <v>80</v>
       </c>
@@ -817,7 +847,7 @@
         <v>井上 由貴</v>
       </c>
       <c r="C18" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G18" s="3" t="str">
         <v>○</v>
@@ -834,7 +864,7 @@
         <v>渋谷 理央</v>
       </c>
       <c r="C19" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J19" s="2">
         <v>59</v>
@@ -848,7 +878,7 @@
         <v>佐々木 春香</v>
       </c>
       <c r="C20" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F20" s="3" t="str">
         <v>×</v>
@@ -867,6 +897,9 @@
       <c r="B21" s="3" t="str">
         <v>高木 和也</v>
       </c>
+      <c r="C21" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J21" s="2">
         <v>83</v>
       </c>
@@ -878,6 +911,9 @@
       <c r="B22" s="3" t="str">
         <v>田村 充</v>
       </c>
+      <c r="C22" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D22" s="3" t="str">
         <v>○</v>
       </c>
@@ -895,6 +931,9 @@
       <c r="B23" s="3" t="str">
         <v>鈴木 亜莉斯</v>
       </c>
+      <c r="C23" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D23" s="3" t="str">
         <v>○</v>
       </c>
@@ -912,6 +951,9 @@
       <c r="B24" s="3" t="str">
         <v>田中 孝司</v>
       </c>
+      <c r="C24" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F24" s="3" t="str">
         <v>○</v>
       </c>
@@ -926,6 +968,9 @@
       <c r="B25" s="3" t="str">
         <v>山田 ジョン</v>
       </c>
+      <c r="C25" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="H25" s="3" t="str">
         <v>〇</v>
       </c>
@@ -941,7 +986,7 @@
         <v>佐藤 幸子</v>
       </c>
       <c r="C26" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J26" s="2">
         <v>83</v>
@@ -955,7 +1000,7 @@
         <v>伊藤 花子</v>
       </c>
       <c r="C27" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D27" s="3" t="str">
         <v>○</v>
@@ -974,6 +1019,9 @@
       <c r="B28" s="3" t="str">
         <v>小林 ジェイク</v>
       </c>
+      <c r="C28" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D28" s="3" t="str">
         <v>○</v>
       </c>
@@ -989,7 +1037,7 @@
         <v>中村 未来</v>
       </c>
       <c r="C29" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="H29" s="3" t="str">
         <v>〇</v>
@@ -1005,6 +1053,9 @@
       <c r="B30" s="3" t="str">
         <v>加藤 琳</v>
       </c>
+      <c r="C30" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F30" s="3" t="str">
         <v>×</v>
       </c>
@@ -1020,7 +1071,7 @@
         <v>斉藤 恵里香</v>
       </c>
       <c r="C31" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D31" s="3" t="str">
         <v>○</v>
@@ -1036,6 +1087,9 @@
       <c r="B32" s="3" t="str">
         <v>三浦 太郎</v>
       </c>
+      <c r="C32" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D32" s="3" t="str">
         <v>○</v>
       </c>
@@ -1054,7 +1108,7 @@
         <v>高橋 絵麻</v>
       </c>
       <c r="C33" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F33" s="3" t="str">
         <v>○</v>
@@ -1071,7 +1125,7 @@
         <v>林 イヴ</v>
       </c>
       <c r="C34" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J34" s="2">
         <v>69</v>
@@ -1084,6 +1138,9 @@
       <c r="B35" s="3" t="str">
         <v>渡辺 怜</v>
       </c>
+      <c r="C35" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J35" s="2">
         <v>75</v>
       </c>
@@ -1096,7 +1153,7 @@
         <v>森田 雄希</v>
       </c>
       <c r="C36" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G36" s="3" t="str">
         <v>○</v>
@@ -1113,7 +1170,7 @@
         <v>山田 真理</v>
       </c>
       <c r="C37" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E37" s="3" t="str">
         <v>○</v>
@@ -1130,7 +1187,7 @@
         <v>井上 翔</v>
       </c>
       <c r="C38" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F38" s="3" t="str">
         <v>×</v>
@@ -1147,7 +1204,7 @@
         <v>渋谷 有紗</v>
       </c>
       <c r="C39" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J39" s="2">
         <v>60</v>
@@ -1160,6 +1217,9 @@
       <c r="B40" s="3" t="str">
         <v>佐々木 賢</v>
       </c>
+      <c r="C40" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G40" s="3" t="str">
         <v>○</v>
       </c>
@@ -1174,6 +1234,9 @@
       <c r="B41" s="3" t="str">
         <v>高木 亜里愛</v>
       </c>
+      <c r="C41" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D41" s="3" t="str">
         <v>○</v>
       </c>
@@ -1188,6 +1251,9 @@
       <c r="B42" s="3" t="str">
         <v>田村 拓真</v>
       </c>
+      <c r="C42" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J42" s="2">
         <v>63</v>
       </c>
@@ -1200,7 +1266,7 @@
         <v>鈴木 美桜</v>
       </c>
       <c r="C43" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F43" s="3" t="str">
         <v>○</v>
@@ -1216,6 +1282,9 @@
       <c r="B44" s="3" t="str">
         <v>山本 健人</v>
       </c>
+      <c r="C44" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D44" s="3" t="str">
         <v>○</v>
       </c>
@@ -1231,7 +1300,7 @@
         <v>佐藤 静香</v>
       </c>
       <c r="C45" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="I45" s="3" t="str">
         <v>〇</v>
@@ -1247,6 +1316,9 @@
       <c r="B46" s="3" t="str">
         <v>伊藤 孝司</v>
       </c>
+      <c r="C46" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J46" s="2">
         <v>69</v>
       </c>
@@ -1259,7 +1331,7 @@
         <v>吉田 恵子</v>
       </c>
       <c r="C47" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J47" s="2">
         <v>62</v>
@@ -1272,6 +1344,9 @@
       <c r="B48" s="3" t="str">
         <v>坂本 拓海</v>
       </c>
+      <c r="C48" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J48" s="2">
         <v>75</v>
       </c>
@@ -1284,7 +1359,7 @@
         <v>川村 理香</v>
       </c>
       <c r="C49" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J49" s="2">
         <v>55</v>
@@ -1297,6 +1372,9 @@
       <c r="B50" s="3" t="str">
         <v>澤田 健治</v>
       </c>
+      <c r="C50" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F50" s="3" t="str">
         <v>×</v>
       </c>
@@ -1311,6 +1389,9 @@
       <c r="B51" s="3" t="str">
         <v>久保 桜</v>
       </c>
+      <c r="C51" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J51" s="2">
         <v>56</v>
       </c>
@@ -1322,6 +1403,9 @@
       <c r="B52" s="3" t="str">
         <v>石井 博士</v>
       </c>
+      <c r="C52" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D52" s="3" t="str">
         <v>○</v>
       </c>
@@ -1336,6 +1420,9 @@
       <c r="B53" s="3" t="str">
         <v>木村 ソフィア</v>
       </c>
+      <c r="C53" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D53" s="3" t="str">
         <v>○</v>
       </c>
@@ -1350,6 +1437,9 @@
       <c r="B54" s="3" t="str">
         <v>佐藤 拓郎</v>
       </c>
+      <c r="C54" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D54" s="3" t="str">
         <v>○</v>
       </c>
@@ -1365,7 +1455,7 @@
         <v>和田 理央</v>
       </c>
       <c r="C55" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J55" s="2">
         <v>81</v>
@@ -1379,7 +1469,7 @@
         <v>石川 光</v>
       </c>
       <c r="C56" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J56" s="2">
         <v>54</v>
@@ -1393,7 +1483,7 @@
         <v>境 泉</v>
       </c>
       <c r="C57" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J57" s="2">
         <v>65</v>
@@ -1407,7 +1497,7 @@
         <v>松田 慶</v>
       </c>
       <c r="C58" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J58" s="2">
         <v>74</v>
@@ -1420,6 +1510,9 @@
       <c r="B59" s="3" t="str">
         <v>中山 孝司</v>
       </c>
+      <c r="C59" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J59" s="2">
         <v>69</v>
       </c>
@@ -1432,7 +1525,7 @@
         <v>山口 小夜</v>
       </c>
       <c r="C60" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J60" s="2">
         <v>77</v>
@@ -1445,6 +1538,9 @@
       <c r="B61" s="3" t="str">
         <v>小川 優太</v>
       </c>
+      <c r="C61" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J61" s="2">
         <v>79</v>
       </c>
@@ -1457,7 +1553,7 @@
         <v>岡田 春樹</v>
       </c>
       <c r="C62" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J62" s="2">
         <v>82</v>
@@ -1471,7 +1567,7 @@
         <v>齋藤 香織</v>
       </c>
       <c r="C63" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J63" s="2">
         <v>86</v>
@@ -1484,6 +1580,9 @@
       <c r="B64" s="3" t="str">
         <v>中沢 慎也</v>
       </c>
+      <c r="C64" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J64" s="2">
         <v>62</v>
       </c>
@@ -1495,6 +1594,9 @@
       <c r="B65" s="3" t="str">
         <v>北村 菊男</v>
       </c>
+      <c r="C65" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J65" s="2">
         <v>86</v>
       </c>
@@ -1507,7 +1609,7 @@
         <v>櫻井 愛</v>
       </c>
       <c r="C66" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J66" s="2">
         <v>89</v>
@@ -1520,6 +1622,9 @@
       <c r="B67" s="3" t="str">
         <v>武田 卓司</v>
       </c>
+      <c r="C67" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J67" s="2">
         <v>91</v>
       </c>
@@ -1532,7 +1637,7 @@
         <v>田辺 玲奈</v>
       </c>
       <c r="C68" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J68" s="2">
         <v>63</v>
@@ -1545,6 +1650,9 @@
       <c r="B69" s="3" t="str">
         <v>石原 裕二</v>
       </c>
+      <c r="C69" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J69" s="2">
         <v>70</v>
       </c>
@@ -1557,7 +1665,7 @@
         <v>白石 真夜</v>
       </c>
       <c r="C70" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J70" s="2">
         <v>80</v>
@@ -1570,6 +1678,9 @@
       <c r="B71" s="3" t="str">
         <v>岩崎 孝</v>
       </c>
+      <c r="C71" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J71" s="2">
         <v>53</v>
       </c>
@@ -1582,7 +1693,7 @@
         <v>佐川 玲子</v>
       </c>
       <c r="C72" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D72" s="3" t="str">
         <v>○</v>
@@ -1598,6 +1709,9 @@
       <c r="B73" s="3" t="str">
         <v>中村 和也</v>
       </c>
+      <c r="C73" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J73" s="2">
         <v>59</v>
       </c>
@@ -1610,7 +1724,7 @@
         <v>浜田 春菜</v>
       </c>
       <c r="C74" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J74" s="2">
         <v>80</v>
@@ -1623,6 +1737,9 @@
       <c r="B75" s="3" t="str">
         <v>森山 圭太</v>
       </c>
+      <c r="C75" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D75" s="3" t="str">
         <v>○</v>
       </c>
@@ -1638,7 +1755,7 @@
         <v>大野 美穂</v>
       </c>
       <c r="C76" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D76" s="3" t="str">
         <v>○</v>
@@ -1654,6 +1771,9 @@
       <c r="B77" s="3" t="str">
         <v>金子 亮</v>
       </c>
+      <c r="C77" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J77" s="2">
         <v>76</v>
       </c>
@@ -1666,7 +1786,7 @@
         <v>前田 真理菜</v>
       </c>
       <c r="C78" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D78" s="3" t="str">
         <v>○</v>
@@ -1683,7 +1803,7 @@
         <v>澤本 香織</v>
       </c>
       <c r="C79" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D79" s="3" t="str">
         <v>○</v>
@@ -1699,6 +1819,9 @@
       <c r="B80" s="3" t="str">
         <v>塩谷 秀樹</v>
       </c>
+      <c r="C80" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J80" s="2">
         <v>70</v>
       </c>
@@ -1711,7 +1834,7 @@
         <v>井上 恵</v>
       </c>
       <c r="C81" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J81" s="2">
         <v>76</v>
@@ -1723,6 +1846,9 @@
       </c>
       <c r="B82" s="3" t="str">
         <v>清水 卓也</v>
+      </c>
+      <c r="C82" s="2" t="str">
+        <v>♂</v>
       </c>
       <c r="J82" s="2">
         <v>74</v>

--- a/public/samples/ja/sample2.xlsx
+++ b/public/samples/ja/sample2.xlsx
@@ -527,7 +527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:K82"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="10.5"/>
   </cols>
@@ -560,6 +560,9 @@
       <c r="J1" s="2">
         <v>1</v>
       </c>
+      <c r="K1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="str">
@@ -592,6 +595,9 @@
       <c r="J2" s="2" t="str">
         <v>テスト平均</v>
       </c>
+      <c r="K2" s="2" t="str">
+        <v>算数の習熟度</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
@@ -609,6 +615,9 @@
       <c r="J3" s="2">
         <v>74</v>
       </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -626,6 +635,9 @@
       <c r="J4" s="2">
         <v>72</v>
       </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -645,6 +657,9 @@
       </c>
       <c r="J5" s="2">
         <v>74</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -663,6 +678,9 @@
       <c r="J6" s="2">
         <v>69</v>
       </c>
+      <c r="K6" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
@@ -680,6 +698,9 @@
       <c r="J7" s="2">
         <v>90</v>
       </c>
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
@@ -694,6 +715,9 @@
       <c r="J8" s="2">
         <v>86</v>
       </c>
+      <c r="K8" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
@@ -711,6 +735,9 @@
       <c r="J9" s="2">
         <v>64</v>
       </c>
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
@@ -728,6 +755,9 @@
       <c r="J10" s="2">
         <v>68</v>
       </c>
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
@@ -742,6 +772,9 @@
       <c r="J11" s="2">
         <v>87</v>
       </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
@@ -759,6 +792,9 @@
       <c r="J12" s="2">
         <v>77</v>
       </c>
+      <c r="K12" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
@@ -776,6 +812,9 @@
       <c r="J13" s="2">
         <v>62</v>
       </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
@@ -790,6 +829,9 @@
       <c r="J14" s="2">
         <v>76</v>
       </c>
+      <c r="K14" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
@@ -807,6 +849,9 @@
       <c r="J15" s="2">
         <v>73</v>
       </c>
+      <c r="K15" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
@@ -824,6 +869,9 @@
       <c r="J16" s="2">
         <v>65</v>
       </c>
+      <c r="K16" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
@@ -838,6 +886,9 @@
       <c r="J17" s="2">
         <v>80</v>
       </c>
+      <c r="K17" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
@@ -855,6 +906,9 @@
       <c r="J18" s="2">
         <v>69</v>
       </c>
+      <c r="K18" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
@@ -869,6 +923,9 @@
       <c r="J19" s="2">
         <v>59</v>
       </c>
+      <c r="K19" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
@@ -889,6 +946,9 @@
       <c r="J20" s="2">
         <v>60</v>
       </c>
+      <c r="K20" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
@@ -903,6 +963,9 @@
       <c r="J21" s="2">
         <v>83</v>
       </c>
+      <c r="K21" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
@@ -923,6 +986,9 @@
       <c r="J22" s="2">
         <v>77</v>
       </c>
+      <c r="K22" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
@@ -943,6 +1009,9 @@
       <c r="J23" s="2">
         <v>67</v>
       </c>
+      <c r="K23" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
@@ -960,6 +1029,9 @@
       <c r="J24" s="2">
         <v>74</v>
       </c>
+      <c r="K24" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
@@ -977,6 +1049,9 @@
       <c r="J25" s="2">
         <v>64</v>
       </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
@@ -991,6 +1066,9 @@
       <c r="J26" s="2">
         <v>83</v>
       </c>
+      <c r="K26" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
@@ -1011,6 +1089,9 @@
       <c r="J27" s="2">
         <v>89</v>
       </c>
+      <c r="K27" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
@@ -1028,6 +1109,9 @@
       <c r="J28" s="2">
         <v>75</v>
       </c>
+      <c r="K28" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
@@ -1045,6 +1129,9 @@
       <c r="J29" s="2">
         <v>54</v>
       </c>
+      <c r="K29" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
@@ -1062,6 +1149,9 @@
       <c r="J30" s="2">
         <v>80</v>
       </c>
+      <c r="K30" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
@@ -1079,6 +1169,9 @@
       <c r="J31" s="2">
         <v>71</v>
       </c>
+      <c r="K31" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
@@ -1099,6 +1192,9 @@
       <c r="J32" s="2">
         <v>60</v>
       </c>
+      <c r="K32" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
@@ -1116,6 +1212,9 @@
       <c r="J33" s="2">
         <v>82</v>
       </c>
+      <c r="K33" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
@@ -1130,6 +1229,9 @@
       <c r="J34" s="2">
         <v>69</v>
       </c>
+      <c r="K34" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
@@ -1144,6 +1246,9 @@
       <c r="J35" s="2">
         <v>75</v>
       </c>
+      <c r="K35" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
@@ -1161,6 +1266,9 @@
       <c r="J36" s="2">
         <v>72</v>
       </c>
+      <c r="K36" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
@@ -1178,6 +1286,9 @@
       <c r="J37" s="2">
         <v>67</v>
       </c>
+      <c r="K37" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
@@ -1195,6 +1306,9 @@
       <c r="J38" s="2">
         <v>81</v>
       </c>
+      <c r="K38" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
@@ -1209,6 +1323,9 @@
       <c r="J39" s="2">
         <v>60</v>
       </c>
+      <c r="K39" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
@@ -1226,6 +1343,9 @@
       <c r="J40" s="2">
         <v>77</v>
       </c>
+      <c r="K40" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
@@ -1243,6 +1363,9 @@
       <c r="J41" s="2">
         <v>84</v>
       </c>
+      <c r="K41" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
@@ -1257,6 +1380,9 @@
       <c r="J42" s="2">
         <v>63</v>
       </c>
+      <c r="K42" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
@@ -1274,6 +1400,9 @@
       <c r="J43" s="2">
         <v>78</v>
       </c>
+      <c r="K43" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
@@ -1291,6 +1420,9 @@
       <c r="J44" s="2">
         <v>50</v>
       </c>
+      <c r="K44" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
@@ -1308,6 +1440,9 @@
       <c r="J45" s="2">
         <v>84</v>
       </c>
+      <c r="K45" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
@@ -1322,6 +1457,9 @@
       <c r="J46" s="2">
         <v>69</v>
       </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
@@ -1336,6 +1474,9 @@
       <c r="J47" s="2">
         <v>62</v>
       </c>
+      <c r="K47" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
@@ -1350,6 +1491,9 @@
       <c r="J48" s="2">
         <v>75</v>
       </c>
+      <c r="K48" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
@@ -1364,6 +1508,9 @@
       <c r="J49" s="2">
         <v>55</v>
       </c>
+      <c r="K49" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
@@ -1381,6 +1528,9 @@
       <c r="J50" s="2">
         <v>65</v>
       </c>
+      <c r="K50" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
@@ -1395,6 +1545,9 @@
       <c r="J51" s="2">
         <v>56</v>
       </c>
+      <c r="K51" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
@@ -1412,6 +1565,9 @@
       <c r="J52" s="2">
         <v>60</v>
       </c>
+      <c r="K52" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
@@ -1429,6 +1585,9 @@
       <c r="J53" s="2">
         <v>63</v>
       </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
@@ -1446,6 +1605,9 @@
       <c r="J54" s="2">
         <v>50</v>
       </c>
+      <c r="K54" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
@@ -1460,6 +1622,9 @@
       <c r="J55" s="2">
         <v>81</v>
       </c>
+      <c r="K55" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
@@ -1474,6 +1639,9 @@
       <c r="J56" s="2">
         <v>54</v>
       </c>
+      <c r="K56" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
@@ -1488,6 +1656,9 @@
       <c r="J57" s="2">
         <v>65</v>
       </c>
+      <c r="K57" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
@@ -1502,6 +1673,9 @@
       <c r="J58" s="2">
         <v>74</v>
       </c>
+      <c r="K58" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
@@ -1516,6 +1690,9 @@
       <c r="J59" s="2">
         <v>69</v>
       </c>
+      <c r="K59" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
@@ -1530,6 +1707,9 @@
       <c r="J60" s="2">
         <v>77</v>
       </c>
+      <c r="K60" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
@@ -1544,6 +1724,9 @@
       <c r="J61" s="2">
         <v>79</v>
       </c>
+      <c r="K61" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
@@ -1558,6 +1741,9 @@
       <c r="J62" s="2">
         <v>82</v>
       </c>
+      <c r="K62" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
@@ -1572,6 +1758,9 @@
       <c r="J63" s="2">
         <v>86</v>
       </c>
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
@@ -1586,6 +1775,9 @@
       <c r="J64" s="2">
         <v>62</v>
       </c>
+      <c r="K64" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
@@ -1600,6 +1792,9 @@
       <c r="J65" s="2">
         <v>86</v>
       </c>
+      <c r="K65" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
@@ -1614,6 +1809,9 @@
       <c r="J66" s="2">
         <v>89</v>
       </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
@@ -1628,6 +1826,9 @@
       <c r="J67" s="2">
         <v>91</v>
       </c>
+      <c r="K67" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
@@ -1642,6 +1843,9 @@
       <c r="J68" s="2">
         <v>63</v>
       </c>
+      <c r="K68" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
@@ -1656,6 +1860,9 @@
       <c r="J69" s="2">
         <v>70</v>
       </c>
+      <c r="K69" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
@@ -1670,6 +1877,9 @@
       <c r="J70" s="2">
         <v>80</v>
       </c>
+      <c r="K70" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
@@ -1684,6 +1894,9 @@
       <c r="J71" s="2">
         <v>53</v>
       </c>
+      <c r="K71" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
@@ -1701,6 +1914,9 @@
       <c r="J72" s="2">
         <v>69</v>
       </c>
+      <c r="K72" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
@@ -1715,6 +1931,9 @@
       <c r="J73" s="2">
         <v>59</v>
       </c>
+      <c r="K73" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
@@ -1729,6 +1948,9 @@
       <c r="J74" s="2">
         <v>80</v>
       </c>
+      <c r="K74" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
@@ -1746,6 +1968,9 @@
       <c r="J75" s="2">
         <v>75</v>
       </c>
+      <c r="K75" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
@@ -1763,6 +1988,9 @@
       <c r="J76" s="2">
         <v>59</v>
       </c>
+      <c r="K76" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
@@ -1777,6 +2005,9 @@
       <c r="J77" s="2">
         <v>76</v>
       </c>
+      <c r="K77" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
@@ -1794,6 +2025,9 @@
       <c r="J78" s="2">
         <v>53</v>
       </c>
+      <c r="K78" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
@@ -1811,6 +2045,9 @@
       <c r="J79" s="2">
         <v>85</v>
       </c>
+      <c r="K79" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
@@ -1825,6 +2062,9 @@
       <c r="J80" s="2">
         <v>70</v>
       </c>
+      <c r="K80" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
@@ -1839,6 +2079,9 @@
       <c r="J81" s="2">
         <v>76</v>
       </c>
+      <c r="K81" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
@@ -1853,11 +2096,14 @@
       <c r="J82" s="2">
         <v>74</v>
       </c>
+      <c r="K82" s="2">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K82"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/public/samples/ja/sample2.xlsx
+++ b/public/samples/ja/sample2.xlsx
@@ -527,7 +527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:K82"/>
   <cols>
     <col min="5" max="5" customWidth="1" width="10.5"/>
   </cols>
@@ -560,6 +560,9 @@
       <c r="J1" s="2">
         <v>1</v>
       </c>
+      <c r="K1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="str">
@@ -569,7 +572,7 @@
         <v>名前</v>
       </c>
       <c r="C2" s="3" t="str">
-        <v>性別♀</v>
+        <v>性別</v>
       </c>
       <c r="D2" s="3" t="str">
         <v>学習支援</v>
@@ -591,6 +594,9 @@
       </c>
       <c r="J2" s="2" t="str">
         <v>テスト平均</v>
+      </c>
+      <c r="K2" s="2" t="str">
+        <v>算数の習熟度</v>
       </c>
     </row>
     <row r="3">
@@ -601,13 +607,16 @@
         <v>田中 綾香</v>
       </c>
       <c r="C3" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D3" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J3" s="2">
         <v>74</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -617,12 +626,18 @@
       <c r="B4" s="3" t="str">
         <v>山本 武志</v>
       </c>
+      <c r="C4" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D4" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J4" s="2">
         <v>72</v>
       </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -632,7 +647,7 @@
         <v>鈴木 美里</v>
       </c>
       <c r="C5" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E5" s="3" t="str">
         <v>○</v>
@@ -642,6 +657,9 @@
       </c>
       <c r="J5" s="2">
         <v>74</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -652,13 +670,16 @@
         <v>佐藤 可奈子</v>
       </c>
       <c r="C6" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G6" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J6" s="2">
         <v>69</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -668,11 +689,17 @@
       <c r="B7" s="3" t="str">
         <v>伊藤 弘樹</v>
       </c>
+      <c r="C7" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G7" s="3" t="str">
         <v>◎</v>
       </c>
       <c r="J7" s="2">
         <v>90</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -682,8 +709,14 @@
       <c r="B8" s="3" t="str">
         <v>小林 優太</v>
       </c>
+      <c r="C8" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J8" s="2">
         <v>86</v>
+      </c>
+      <c r="K8" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -693,11 +726,17 @@
       <c r="B9" s="3" t="str">
         <v>中村 芽衣</v>
       </c>
+      <c r="C9" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G9" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J9" s="2">
         <v>64</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -707,11 +746,17 @@
       <c r="B10" s="3" t="str">
         <v>加藤 信次</v>
       </c>
+      <c r="C10" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="H10" s="3" t="str">
         <v>〇</v>
       </c>
       <c r="J10" s="2">
         <v>68</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -722,10 +767,13 @@
         <v>斉藤 まどか</v>
       </c>
       <c r="C11" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J11" s="2">
         <v>87</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -735,11 +783,17 @@
       <c r="B12" s="3" t="str">
         <v>三浦 太一</v>
       </c>
+      <c r="C12" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D12" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J12" s="2">
         <v>77</v>
+      </c>
+      <c r="K12" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -750,13 +804,16 @@
         <v>高橋 直美</v>
       </c>
       <c r="C13" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G13" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J13" s="2">
         <v>62</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -766,8 +823,14 @@
       <c r="B14" s="3" t="str">
         <v>林 健治</v>
       </c>
+      <c r="C14" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J14" s="2">
         <v>76</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -777,11 +840,17 @@
       <c r="B15" s="3" t="str">
         <v>渡辺 明良</v>
       </c>
+      <c r="C15" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F15" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J15" s="2">
         <v>73</v>
+      </c>
+      <c r="K15" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -791,11 +860,17 @@
       <c r="B16" s="3" t="str">
         <v>森田 愛</v>
       </c>
+      <c r="C16" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="E16" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J16" s="2">
         <v>65</v>
+      </c>
+      <c r="K16" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -805,8 +880,14 @@
       <c r="B17" s="3" t="str">
         <v>山田 孝史</v>
       </c>
+      <c r="C17" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J17" s="2">
         <v>80</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -817,13 +898,16 @@
         <v>井上 由貴</v>
       </c>
       <c r="C18" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G18" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J18" s="2">
         <v>69</v>
+      </c>
+      <c r="K18" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -834,10 +918,13 @@
         <v>渋谷 理央</v>
       </c>
       <c r="C19" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J19" s="2">
         <v>59</v>
+      </c>
+      <c r="K19" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -848,7 +935,7 @@
         <v>佐々木 春香</v>
       </c>
       <c r="C20" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F20" s="3" t="str">
         <v>×</v>
@@ -858,6 +945,9 @@
       </c>
       <c r="J20" s="2">
         <v>60</v>
+      </c>
+      <c r="K20" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -867,8 +957,14 @@
       <c r="B21" s="3" t="str">
         <v>高木 和也</v>
       </c>
+      <c r="C21" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J21" s="2">
         <v>83</v>
+      </c>
+      <c r="K21" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -878,6 +974,9 @@
       <c r="B22" s="3" t="str">
         <v>田村 充</v>
       </c>
+      <c r="C22" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D22" s="3" t="str">
         <v>○</v>
       </c>
@@ -886,6 +985,9 @@
       </c>
       <c r="J22" s="2">
         <v>77</v>
+      </c>
+      <c r="K22" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -895,6 +997,9 @@
       <c r="B23" s="3" t="str">
         <v>鈴木 亜莉斯</v>
       </c>
+      <c r="C23" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D23" s="3" t="str">
         <v>○</v>
       </c>
@@ -903,6 +1008,9 @@
       </c>
       <c r="J23" s="2">
         <v>67</v>
+      </c>
+      <c r="K23" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -912,11 +1020,17 @@
       <c r="B24" s="3" t="str">
         <v>田中 孝司</v>
       </c>
+      <c r="C24" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F24" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J24" s="2">
         <v>74</v>
+      </c>
+      <c r="K24" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -926,11 +1040,17 @@
       <c r="B25" s="3" t="str">
         <v>山田 ジョン</v>
       </c>
+      <c r="C25" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="H25" s="3" t="str">
         <v>〇</v>
       </c>
       <c r="J25" s="2">
         <v>64</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -941,10 +1061,13 @@
         <v>佐藤 幸子</v>
       </c>
       <c r="C26" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J26" s="2">
         <v>83</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -955,7 +1078,7 @@
         <v>伊藤 花子</v>
       </c>
       <c r="C27" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D27" s="3" t="str">
         <v>○</v>
@@ -965,6 +1088,9 @@
       </c>
       <c r="J27" s="2">
         <v>89</v>
+      </c>
+      <c r="K27" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -974,11 +1100,17 @@
       <c r="B28" s="3" t="str">
         <v>小林 ジェイク</v>
       </c>
+      <c r="C28" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D28" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J28" s="2">
         <v>75</v>
+      </c>
+      <c r="K28" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -989,13 +1121,16 @@
         <v>中村 未来</v>
       </c>
       <c r="C29" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="H29" s="3" t="str">
         <v>〇</v>
       </c>
       <c r="J29" s="2">
         <v>54</v>
+      </c>
+      <c r="K29" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1005,11 +1140,17 @@
       <c r="B30" s="3" t="str">
         <v>加藤 琳</v>
       </c>
+      <c r="C30" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F30" s="3" t="str">
         <v>×</v>
       </c>
       <c r="J30" s="2">
         <v>80</v>
+      </c>
+      <c r="K30" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1020,13 +1161,16 @@
         <v>斉藤 恵里香</v>
       </c>
       <c r="C31" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D31" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J31" s="2">
         <v>71</v>
+      </c>
+      <c r="K31" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1036,6 +1180,9 @@
       <c r="B32" s="3" t="str">
         <v>三浦 太郎</v>
       </c>
+      <c r="C32" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D32" s="3" t="str">
         <v>○</v>
       </c>
@@ -1044,6 +1191,9 @@
       </c>
       <c r="J32" s="2">
         <v>60</v>
+      </c>
+      <c r="K32" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1054,13 +1204,16 @@
         <v>高橋 絵麻</v>
       </c>
       <c r="C33" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F33" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J33" s="2">
         <v>82</v>
+      </c>
+      <c r="K33" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1071,10 +1224,13 @@
         <v>林 イヴ</v>
       </c>
       <c r="C34" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J34" s="2">
         <v>69</v>
+      </c>
+      <c r="K34" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1084,8 +1240,14 @@
       <c r="B35" s="3" t="str">
         <v>渡辺 怜</v>
       </c>
+      <c r="C35" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J35" s="2">
         <v>75</v>
+      </c>
+      <c r="K35" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -1096,13 +1258,16 @@
         <v>森田 雄希</v>
       </c>
       <c r="C36" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G36" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J36" s="2">
         <v>72</v>
+      </c>
+      <c r="K36" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1113,13 +1278,16 @@
         <v>山田 真理</v>
       </c>
       <c r="C37" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E37" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J37" s="2">
         <v>67</v>
+      </c>
+      <c r="K37" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1130,13 +1298,16 @@
         <v>井上 翔</v>
       </c>
       <c r="C38" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F38" s="3" t="str">
         <v>×</v>
       </c>
       <c r="J38" s="2">
         <v>81</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1147,10 +1318,13 @@
         <v>渋谷 有紗</v>
       </c>
       <c r="C39" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J39" s="2">
         <v>60</v>
+      </c>
+      <c r="K39" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1160,11 +1334,17 @@
       <c r="B40" s="3" t="str">
         <v>佐々木 賢</v>
       </c>
+      <c r="C40" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G40" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J40" s="2">
         <v>77</v>
+      </c>
+      <c r="K40" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -1174,11 +1354,17 @@
       <c r="B41" s="3" t="str">
         <v>高木 亜里愛</v>
       </c>
+      <c r="C41" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D41" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J41" s="2">
         <v>84</v>
+      </c>
+      <c r="K41" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1188,8 +1374,14 @@
       <c r="B42" s="3" t="str">
         <v>田村 拓真</v>
       </c>
+      <c r="C42" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J42" s="2">
         <v>63</v>
+      </c>
+      <c r="K42" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -1200,13 +1392,16 @@
         <v>鈴木 美桜</v>
       </c>
       <c r="C43" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F43" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J43" s="2">
         <v>78</v>
+      </c>
+      <c r="K43" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1216,11 +1411,17 @@
       <c r="B44" s="3" t="str">
         <v>山本 健人</v>
       </c>
+      <c r="C44" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D44" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J44" s="2">
         <v>50</v>
+      </c>
+      <c r="K44" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1231,13 +1432,16 @@
         <v>佐藤 静香</v>
       </c>
       <c r="C45" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="I45" s="3" t="str">
         <v>〇</v>
       </c>
       <c r="J45" s="2">
         <v>84</v>
+      </c>
+      <c r="K45" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1247,8 +1451,14 @@
       <c r="B46" s="3" t="str">
         <v>伊藤 孝司</v>
       </c>
+      <c r="C46" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J46" s="2">
         <v>69</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1259,10 +1469,13 @@
         <v>吉田 恵子</v>
       </c>
       <c r="C47" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J47" s="2">
         <v>62</v>
+      </c>
+      <c r="K47" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1272,8 +1485,14 @@
       <c r="B48" s="3" t="str">
         <v>坂本 拓海</v>
       </c>
+      <c r="C48" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J48" s="2">
         <v>75</v>
+      </c>
+      <c r="K48" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -1284,10 +1503,13 @@
         <v>川村 理香</v>
       </c>
       <c r="C49" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J49" s="2">
         <v>55</v>
+      </c>
+      <c r="K49" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -1297,11 +1519,17 @@
       <c r="B50" s="3" t="str">
         <v>澤田 健治</v>
       </c>
+      <c r="C50" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F50" s="3" t="str">
         <v>×</v>
       </c>
       <c r="J50" s="2">
         <v>65</v>
+      </c>
+      <c r="K50" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1311,8 +1539,14 @@
       <c r="B51" s="3" t="str">
         <v>久保 桜</v>
       </c>
+      <c r="C51" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J51" s="2">
         <v>56</v>
+      </c>
+      <c r="K51" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1322,11 +1556,17 @@
       <c r="B52" s="3" t="str">
         <v>石井 博士</v>
       </c>
+      <c r="C52" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D52" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J52" s="2">
         <v>60</v>
+      </c>
+      <c r="K52" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1336,11 +1576,17 @@
       <c r="B53" s="3" t="str">
         <v>木村 ソフィア</v>
       </c>
+      <c r="C53" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D53" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J53" s="2">
         <v>63</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1350,11 +1596,17 @@
       <c r="B54" s="3" t="str">
         <v>佐藤 拓郎</v>
       </c>
+      <c r="C54" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D54" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J54" s="2">
         <v>50</v>
+      </c>
+      <c r="K54" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1365,10 +1617,13 @@
         <v>和田 理央</v>
       </c>
       <c r="C55" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J55" s="2">
         <v>81</v>
+      </c>
+      <c r="K55" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1379,10 +1634,13 @@
         <v>石川 光</v>
       </c>
       <c r="C56" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J56" s="2">
         <v>54</v>
+      </c>
+      <c r="K56" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1393,10 +1651,13 @@
         <v>境 泉</v>
       </c>
       <c r="C57" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J57" s="2">
         <v>65</v>
+      </c>
+      <c r="K57" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1407,10 +1668,13 @@
         <v>松田 慶</v>
       </c>
       <c r="C58" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J58" s="2">
         <v>74</v>
+      </c>
+      <c r="K58" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -1420,8 +1684,14 @@
       <c r="B59" s="3" t="str">
         <v>中山 孝司</v>
       </c>
+      <c r="C59" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J59" s="2">
         <v>69</v>
+      </c>
+      <c r="K59" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1432,10 +1702,13 @@
         <v>山口 小夜</v>
       </c>
       <c r="C60" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J60" s="2">
         <v>77</v>
+      </c>
+      <c r="K60" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1445,8 +1718,14 @@
       <c r="B61" s="3" t="str">
         <v>小川 優太</v>
       </c>
+      <c r="C61" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J61" s="2">
         <v>79</v>
+      </c>
+      <c r="K61" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -1457,10 +1736,13 @@
         <v>岡田 春樹</v>
       </c>
       <c r="C62" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J62" s="2">
         <v>82</v>
+      </c>
+      <c r="K62" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1471,10 +1753,13 @@
         <v>齋藤 香織</v>
       </c>
       <c r="C63" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J63" s="2">
         <v>86</v>
+      </c>
+      <c r="K63" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1484,8 +1769,14 @@
       <c r="B64" s="3" t="str">
         <v>中沢 慎也</v>
       </c>
+      <c r="C64" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J64" s="2">
         <v>62</v>
+      </c>
+      <c r="K64" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -1495,8 +1786,14 @@
       <c r="B65" s="3" t="str">
         <v>北村 菊男</v>
       </c>
+      <c r="C65" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J65" s="2">
         <v>86</v>
+      </c>
+      <c r="K65" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -1507,10 +1804,13 @@
         <v>櫻井 愛</v>
       </c>
       <c r="C66" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J66" s="2">
         <v>89</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1520,8 +1820,14 @@
       <c r="B67" s="3" t="str">
         <v>武田 卓司</v>
       </c>
+      <c r="C67" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J67" s="2">
         <v>91</v>
+      </c>
+      <c r="K67" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1532,10 +1838,13 @@
         <v>田辺 玲奈</v>
       </c>
       <c r="C68" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J68" s="2">
         <v>63</v>
+      </c>
+      <c r="K68" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -1545,8 +1854,14 @@
       <c r="B69" s="3" t="str">
         <v>石原 裕二</v>
       </c>
+      <c r="C69" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J69" s="2">
         <v>70</v>
+      </c>
+      <c r="K69" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -1557,10 +1872,13 @@
         <v>白石 真夜</v>
       </c>
       <c r="C70" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J70" s="2">
         <v>80</v>
+      </c>
+      <c r="K70" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -1570,8 +1888,14 @@
       <c r="B71" s="3" t="str">
         <v>岩崎 孝</v>
       </c>
+      <c r="C71" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J71" s="2">
         <v>53</v>
+      </c>
+      <c r="K71" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -1582,13 +1906,16 @@
         <v>佐川 玲子</v>
       </c>
       <c r="C72" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D72" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J72" s="2">
         <v>69</v>
+      </c>
+      <c r="K72" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -1598,8 +1925,14 @@
       <c r="B73" s="3" t="str">
         <v>中村 和也</v>
       </c>
+      <c r="C73" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J73" s="2">
         <v>59</v>
+      </c>
+      <c r="K73" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -1610,10 +1943,13 @@
         <v>浜田 春菜</v>
       </c>
       <c r="C74" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J74" s="2">
         <v>80</v>
+      </c>
+      <c r="K74" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -1623,11 +1959,17 @@
       <c r="B75" s="3" t="str">
         <v>森山 圭太</v>
       </c>
+      <c r="C75" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D75" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J75" s="2">
         <v>75</v>
+      </c>
+      <c r="K75" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -1638,13 +1980,16 @@
         <v>大野 美穂</v>
       </c>
       <c r="C76" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D76" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J76" s="2">
         <v>59</v>
+      </c>
+      <c r="K76" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -1654,8 +1999,14 @@
       <c r="B77" s="3" t="str">
         <v>金子 亮</v>
       </c>
+      <c r="C77" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J77" s="2">
         <v>76</v>
+      </c>
+      <c r="K77" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -1666,13 +2017,16 @@
         <v>前田 真理菜</v>
       </c>
       <c r="C78" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D78" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J78" s="2">
         <v>53</v>
+      </c>
+      <c r="K78" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -1683,13 +2037,16 @@
         <v>澤本 香織</v>
       </c>
       <c r="C79" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D79" s="3" t="str">
         <v>○</v>
       </c>
       <c r="J79" s="2">
         <v>85</v>
+      </c>
+      <c r="K79" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -1699,8 +2056,14 @@
       <c r="B80" s="3" t="str">
         <v>塩谷 秀樹</v>
       </c>
+      <c r="C80" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J80" s="2">
         <v>70</v>
+      </c>
+      <c r="K80" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -1711,10 +2074,13 @@
         <v>井上 恵</v>
       </c>
       <c r="C81" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="J81" s="2">
         <v>76</v>
+      </c>
+      <c r="K81" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -1724,14 +2090,20 @@
       <c r="B82" s="3" t="str">
         <v>清水 卓也</v>
       </c>
+      <c r="C82" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="J82" s="2">
         <v>74</v>
+      </c>
+      <c r="K82" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K82"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
